--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/00_enterprise_profile.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/00_enterprise_profile.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rdfa141139f7b4cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R44721c5821094d3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Re13d2600b5204152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R576bcb3ebba84a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R3733ea202061498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R437a71b48f9f4401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rcf6b4d70cb8e44a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R09ba0764b6e449f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3e340b4d064a45eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R23893854acb24434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8aabde05ff0c465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rd106c551492c4150"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -630,7 +630,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R855be25b39454ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb0a5a575e2641cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -821,7 +821,7 @@
         <x:v>CEO; CIO; CDAO; CFO; COO; CMO; Health Plan COO</x:v>
       </x:c>
       <x:c r="P6" s="78" t="str">
-        <x:v>Validate headquarters, precise revenue, employee count, named leaders, operating KPIs, and active platform ownership with client evidence.</x:v>
+        <x:v>Validate selected record (record 1) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q6" s="41" t="str">
         <x:v>High</x:v>
@@ -858,7 +858,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b572cf42958424b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8b333c86bbd4364"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -988,7 +988,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fb1a0b8346541d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68f19f0d992444c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1192,7 +1192,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6491d86a2e1a40bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc8e6b0b722843ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1246,7 +1246,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf52bd8b59da4ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra897049deb104bef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1356,7 +1356,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cc733645ac946ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54903444877e4346"/>
   </x:tableParts>
 </x:worksheet>
 </file>